--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A331"/>
+  <dimension ref="A1:A263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,35 +438,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
+          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/usibc-la-waves-summit-requested-netflix-to-provide-space-for-marathi-content-on-platform-says-maharashtra-cultural-affairs-minister-ashish-shelar-23587606</t>
+          <t>https://timesofindia.indiatimes.com/india/culture-push-at-aoi-as-maharashtra-minister-announces-new-art-award/articleshow/118311062.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/usibc-la-waves-summit-requested-netflix-to-provide-space-for-marathi-content-on-platform-says-maharashtra-cultural-affairs-minister-ashish-shelar-23587606</t>
         </is>
       </c>
     </row>
@@ -494,42 +494,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
+          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
+          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ashish-shelar-gets-coveted-malabar-hill-bungalow-101736364223566.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ashish-shelar-gets-coveted-malabar-hill-bungalow-101736364223566.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
+          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
         </is>
       </c>
     </row>
@@ -543,546 +543,546 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
+          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganeshotsav-is-a-powerful-symbol-of-hindutva-ashish-shelar-101753039758492.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
+          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ganeshotsav-is-a-powerful-symbol-of-hindutva-ashish-shelar-101753039758492.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ahead-of-bmc-polls-bjp-asks-review-reports-from-party-members-101751138056408.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ahead-of-bmc-polls-bjp-asks-review-reports-from-party-members-101751138056408.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/shelar-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra/ar-AA1L1WDR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ashish-shelar-3359084</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
+          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ashish-shelar-3359084</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
+          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
+          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
+          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
+          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
+          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://travel.economictimes.indiatimes.com/news/destination/states/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-maha-minister/117794576</t>
+          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/firebrand-legislator-and-fadnavis-confidante-ameet-satam-made-bjps-mumbai-chiefahead-of-bmc-polls-3696247</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
+          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
+          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
+          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
+          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/dont-question-capabilities-of-marathi-speakers-bjp-minister-shelar-after-dubey-remarks/2682767/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
+          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-orders-cultural-dept-probe-absconding-ranveer-allahbadia-to-face-cops-today-all-you-need-to-know/articleshow/118267899.cms</t>
+          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
+          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
+          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
+          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
+          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
+          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507/</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
+          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/reclassify-sgnp-slums-land-as-non-forest-to-avoid-relocation/articleshow/121523748.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-grants-maharashtra-state-festival-status-to-ganeshotsav-promises-funds/articleshow/122373114.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
+          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
         </is>
       </c>
     </row>
@@ -1124,301 +1124,301 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
+          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.bwpeople.in/article/ameet-satam-appointed-bjp-mumbai-chief-ahead-of-polls-568808</t>
+          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
+          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
+          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Highlight-power-of-Operation-Sindoor-during-Ganesh-festival--Shelar-tells-organisers/2841354</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
+          <t>https://www.ptinews.com/story/national/highlight-power-of-operation-sindoor-during-ganesh-festival-shelar-tells-organisers/2841354</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
+          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
+          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
+          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6712027</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-government-selects-savarkar-composition-for-its-1st-sambhaji-maharaj-song-award-enn25022600100</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
+          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-sinhagad-fort-development-plan-meeting-to-be-held-within-15-days-says-cultural-minister-ashish-shelar/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack/</t>
+          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
+          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
+          <t>https://www.socialnews.xyz/?p=6712027</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/50-marathi-teaching-schools-in-america-support-promised-with-curriculum-and-recommendations-to-over-50-schools-teaching-nearly-300-students-135526242.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
+          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
+          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
+          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
+          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
+          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
+          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
+          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
+          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
         </is>
       </c>
     </row>
@@ -1432,1316 +1432,840 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3548452-maharashtras-ganesh-festival-celebrating-indias-valor</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
+          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/bjp-likely-to-appoint-new-mumbai-chief-ahead-of-bmc-polls-13375950.html</t>
+          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
+          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/industry-briefing-news/ameet-satam-appointed-bjp-mumbai-chief-146770.html</t>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://uniindia.com/no-one-wants-to-stay-in-shiv-sena-ubt--bjp/west/news/3496190.html</t>
+          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3601925-amit-satam-takes-charge-as-mumbai-bjp-president-ahead-of-crucial-bmc-elections</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/reema-lagoo-s-ex-huband-vivek-lagoo-no-more-6939671.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/sword-of-maratha-glory-returns-after-two-centuries-maharashtra-brings-home-raghuji-bhosales-legendary-weapon-from-london-auction-135656002.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
+          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
+          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/entertainment/marathi/movies/news/4-marathi-films-selected-for-cannes-film-festival-minister/articleshow/120451522.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dispute-between-bjp-party-workers-in-front-of-minister-ashish-shelar-car/articleshow/121829032.cms</t>
+          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
+          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
+          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
+          <t>https://mahasamvad.in/176545/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
+          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-demand-to-asi-central-government-to-handover-forts-to-maharashtra-govt-raigad-archaeological-survey-of-india-marathi-news-1351013</t>
+          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/4066-new-aadhaar-kits-will-be-given-to-district-collectors-by-information-technology-department-says-ashish-shelar-how-much-in-your-district-1341609</t>
+          <t>https://mahasamvad.in/176672/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/amit-thackeray-meets-ashish-shelar-amid-mns-shiv-sena-ubt-alliance-talks-on-raj-thackeray-uddhav-thackeray/articleshow/123466514.cms</t>
+          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
+          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
+          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
+          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
+          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
+          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
+          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
+          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
+          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
+          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
+          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
+          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
+          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
+          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
+          <t>https://mahasamvad.in/165514/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154669/</t>
+          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
+          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
+          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
+          <t>https://mahasamvad.in/159784/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/amit-thackeray-meet-ashish-shelar-bjp-minister-mns-party-leader/914757/</t>
+          <t>https://mahasamvad.in/160573/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176545/</t>
+          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
+          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ashish-shelar-mocks-mns-leader-prakash-mahajan-raj-thackeray-friendship-1389288.html</t>
+          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176672/</t>
+          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment/articleshow/120695379.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/thackeray-father-and-son-meet-bjp-leaders-what-is-the-real-reason-281903/amp/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
+          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
+          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
+          <t>https://mahasamvad.in/157961/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
+          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
+          <t>https://mahasamvad.in/158808/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-at-aaditya-thackeray-constituency-in-worli-maharashtra-politics-abp-majha-1361553</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
+          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
+          <t>https://marathi.ndtv.com/maharashtra/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-ai-university-and-employment-shortage-9153869</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
+          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
+          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
+          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
+          <t>https://mahasamvad.in/163660/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
+          <t>https://mahasamvad.in/175532/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-election-commission-allegations-devendra-fadnavis-ashish-shelar-response-2025-08-07</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
+          <t>https://mahasamvad.in/160568/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165514/</t>
+          <t>https://mahasamvad.in/174804/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
+          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
+          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
+          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-parties-try-to-woo-ganpati-devotees-with-free-travel-101756094947074.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160573/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/243-roads-dug-up-in-h-west-ward-many-utilities-damaged-101738523195660.html</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
+          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159784/</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
+          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
+          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
+          <t>https://timesofindia.indiatimes.com/india/washing-powder-formula-again-uddhav-thackeray-asks-did-the-pahalgam-terrorists-join-bjp-amid-hindi-vs-marathi-row/articleshow/122297598.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
+          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
+          <t>https://www.indiatoday.in/elections/assembly/video/video-pm-pauses-delhi-victory-speech-to-check-on-unwell-bjp-worker-in-audience-2676959-2025-02-08</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
+          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-ganeshotsav-declared-state-festival-of-maharashtra-minister-ashish-shelar-expressed-happiness-news-hindi-1-735521-KKN.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/videos/news/india-special-report-ashish-shelar-bjp-slams-on-uddhav-thackeray-shivsena-maharashtra-politics-abp-majha-1355752</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/chandrapur/congress-leader-vijay-wadettiwar-met-bjp-leader-and-minister-ashish-shelar-in-chandrapur-marathi-news/articleshow/119940732.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sanjay-raut-talk-on-ashish-shelar-statement-about-friendship-with-raj-thackeray-news-in-marathi/articleshow/120507660.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>https://inshorts.com/en/news/hindus-in-pahalgam-killed-over-religion--over-language-in-maha--shelar-1751789540577</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/175532/</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/174804/</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/160568/</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mumbai/marathi-film-katta-was-launched-by-ashish-shelar/844408/</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-declare-aaple-sarkar-numbers-increased-in-maharashtra-and-also-rates-also-modified-marathi-news-1351214</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-criticizes-uddhav-thackeray-wears-rudraksha-mala-to-his-rally-and-chants-aurangzeb-mantra-maharashtra-politics-marathi-news-1346679</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/entertainment/singer-asha-bhosle-on-raj-thackrey-uddhav-thackrey-togater-she-says-i-only-know-ashish-shelar-i-don-t-know-any-other-politician-1366511</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chhatrapati-shivaji-maharaj-fort-place-on-the-world-heritage-list-minister-ashish-shelar-said/articleshow/118510900.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/live-telecast-of-ganeshotsav-events-minister/articleshow/122770675.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>https://www.jansatta.com/national/mumbai-bjp-new-president-appointed-three-time-mla-ameet-satam-bmc-elections-big-challenge/4109409/</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/hi/!bharat/ahead-of-bmc-polls-mla-ameet-satam-named-new-mumbai-bjp-chief-hindi-news-hin25082501591</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-officially-declares-ganeshotsav-as-state-festival-cultural-heritage-emphasized-201752157149955.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>https://thecsrjournal.in/maharashtra-declares-ganeshotsav-as-state-festival-hindi/</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>https://www.indiatv.in/maharashtra/devendra-fadnavis-govt-declare-ganesh-festival-as-maharashtra-state-festival-2025-07-10-1148320</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-andheri-west-mla-ameet-satam-appointed-mumbai-bjp-chief-ahead-of-bmc-polls-know-all/articleshow/123499476.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>https://www.jansatta.com/national/ganpati-festival-becomes-maharashtra-state-festival-fadnavis-government-will-bear-expenses-of-program/4040819/</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-devendra-fadnavis-govt-also-participates-in-ganeshotsav-2025-made-a-big-announcement/articleshow/122785708.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/savarkar-song-anadi-me-anant-me-gets-inspirational-song-award-maharashtra-government-makes-a-big-announcement-ntc-dskc-2176549-2025-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>https://hindicurrentaffairs.adda247.com/maharashtra-government-declares-ganeshotsav-as-state-festival/</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>https://lalluram.com/rahul-gandhis-brain-chip-stolen-and-hard-disk-corrupted/</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>https://dainiksaveratimes.com/big-1/ganeshotsav-gets-status-state-festival-in-maharashtra-fadnavis-government/</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>https://hindi.latestly.com/lifestyle/festivals-events/ganeshotsav-now-maharashtras-official-state-festival-govt-to-fund-celebrations-2689983.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>https://bharat24live.com/news/devajit-saikia-replaces-jay-shah-as-bcci-secretary</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+          <t>https://aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452/</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A263"/>
+  <dimension ref="A1:A323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,21 +438,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
+          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
@@ -494,21 +494,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
+          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
+          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
         </is>
       </c>
     </row>
@@ -522,98 +522,98 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
+          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
+          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ganeshotsav-is-a-powerful-symbol-of-hindutva-ashish-shelar-101753039758492.html</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganeshotsav-is-a-powerful-symbol-of-hindutva-ashish-shelar-101753039758492.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
+          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
         </is>
       </c>
     </row>
@@ -627,112 +627,112 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
+          <t>http://www.msn.com/en-in/news/India/shelar-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra/ar-AA1L1WDR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ashish-shelar-3359084</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ashish-shelar-3359084</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
+          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
         </is>
       </c>
     </row>
@@ -753,427 +753,427 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
+          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/firebrand-legislator-and-fadnavis-confidante-ameet-satam-made-bjps-mumbai-chiefahead-of-bmc-polls-3696247</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
+          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
+          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
+          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-grants-maharashtra-state-festival-status-to-ganeshotsav-promises-funds/articleshow/122373114.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-orders-cultural-dept-probe-absconding-ranveer-allahbadia-to-face-cops-today-all-you-need-to-know/articleshow/118267899.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
+          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
+          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
+          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507</t>
+          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
+          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
+          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
+          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
+          <t>https://www.dtnext.in/entertainment/cinema/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-842675</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
+          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
+          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
+          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
+          <t>https://www.deccanherald.com/india/maharashtra/cm-fadnavis-to-be-guardian-minister-of-gadchiroli-dhananjay-munde-not-in-list-3362163</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
+          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
         </is>
       </c>
     </row>
@@ -1187,1085 +1187,1505 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/highlight-power-of-operation-sindoor-during-ganesh-festival-shelar-tells-organisers/2841354</t>
+          <t>https://www.bwpeople.in/article/ameet-satam-appointed-bjp-mumbai-chief-ahead-of-polls-568808</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
+          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
+          <t>https://www.thestatesman.com/india/uddhav-thackeray-rohit-pawar-hit-back-after-bjp-ministers-terrorist-remark-1503454822.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-government-selects-savarkar-composition-for-its-1st-sambhaji-maharaj-song-award-enn25022600100</t>
+          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609/</t>
+          <t>https://www.exchange4media.com/industry-briefing-news/ameet-satam-appointed-bjp-mumbai-chief-146770.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
+          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
+          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6712027</t>
+          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/50-marathi-teaching-schools-in-america-support-promised-with-curriculum-and-recommendations-to-over-50-schools-teaching-nearly-300-students-135526242.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
+          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
+          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
+          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
+          <t>https://www.socialnews.xyz/?p=6712027</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
+          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
+          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
+          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
+          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
+          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
+          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
+          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
+          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3548452-maharashtras-ganesh-festival-celebrating-indias-valor</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
+          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
+          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
+          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
+          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
+          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
+          <t>http://www.msn.com/en-in/entertainment/bollywood/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/ar-AA1K6y4Q?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
+          <t>https://www.cnbctv18.com/travel/culture/dahi-handi-on-august-16-maharashtra-govt-has-a-unique-gift-for-1-5-lakh-govindas-19639524.htm</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994828609/Forest-department-officials-suddenly-reached-Shahrukh-Khans-house-Mannat-Maharashtra-government-got-angry-</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/sword-of-maratha-glory-returns-after-two-centuries-maharashtra-brings-home-raghuji-bhosales-legendary-weapon-from-london-auction-135656002.html</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/bandra-ganeshotsav-mandal-kashi-vishwanath-temple-replica-celebrates-ahilyabai-holkar-300-birth-anniversary-rajya-mahotsav-135765190.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
+          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
+          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
+          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
+          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
+          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176545/</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/geeta-gawli-meet-ashish-shelar-mumbai-gangster-arun-gawli-daughter-daughter-bjp-meeting-bmc-election-marathi-news-1364407</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176672/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ashish-shelar-slams-mns-raj-thackeray-on-hindi-language-compulsory-in-maharashtra-school-curriculum-1386802.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
+          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
+          <t>https://marathi.abplive.com/tv-show/special-report/devendra-fadanvis-asha-bhosale-ashish-shelar-radio-mhotsav-special-report-marathi-news-abp-majha-1365435</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
+          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
+          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
+          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
+          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165514/</t>
+          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
+          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
+          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159784/</t>
+          <t>https://www.loksatta.com/mumbai/bandra-kurla-railway-alignment-cancelled-controversy-ashish-shelar-orders-report-to-mmrda-mumbai-print-news-vsd-99-5174076/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160573/</t>
+          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
+          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
+          <t>https://mahasamvad.in/176545/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
+          <t>https://www.lokmat.com/shorts/mumbai/bjp-s-jai-veeru-to-challenge-thackeray-brothers-in-mumbai-municipal-elections/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
+          <t>https://mahasamvad.in/176672/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
+          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment/articleshow/120695379.cms</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
+          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
+          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
+          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
+          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157961/</t>
+          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158808/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-at-aaditya-thackeray-constituency-in-worli-maharashtra-politics-abp-majha-1361553</t>
+          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
+          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-ai-university-and-employment-shortage-9153869</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
+          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
+          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
+          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163660/</t>
+          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175532/</t>
+          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
+          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160568/</t>
+          <t>https://mahasamvad.in/165514/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174804/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
+          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
+          <t>https://mahasamvad.in/159784/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
+          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
+          <t>https://mahasamvad.in/160573/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-parties-try-to-woo-ganpati-devotees-with-free-travel-101756094947074.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-ameet-satam-anheri-mla-is-mumbai-bjp-chief-took-place-of-ashish-shelar-know-detail-story-9547057.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
+          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/243-roads-dug-up-in-h-west-ward-many-utilities-damaged-101738523195660.html</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-cultural-center-and-museum-to-be-set-up-in-bkc-mumbai-said-minister-ashish-shelar-in-assembly-budget-session-2025-maharashtra-news-mhs25031900644</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
+          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
+          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
+          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/washing-powder-formula-again-uddhav-thackeray-asks-did-the-pahalgam-terrorists-join-bjp-amid-hindi-vs-marathi-row/articleshow/122297598.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/elections/assembly/video/video-pm-pauses-delhi-victory-speech-to-check-on-unwell-bjp-worker-in-audience-2676959-2025-02-08</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
+          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/158808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/157961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/12-forts-of-chhatrapati-shivaji-maharaj-included-in-unesco-world-heritage-list-congratulatory-resolution-passed-in-maharashtra-legislative-council-maharashtra-news-mhs25071404363</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/news/one-s-speech-is-incomplete-and-the-other-s-is-irrelevant-ashish-shelar-s-criticism-of-the-thackeray-brothers-rally/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/175532/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/163660/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/160568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/politics-mumbai-bjp-president-race-ashish-shelar-emerges-as-frontrunner-for-bmc-elections-1367226</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/amit-thackeray-meets-ashish-shelar-amid-mns-shiv-sena-ubt-alliance-talks-on-raj-thackeray-uddhav-thackeray/articleshow/123466514.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chhatrapati-shivaji-maharaj-fort-place-on-the-world-heritage-list-minister-ashish-shelar-said/articleshow/118510900.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/entertainment/singer-asha-bhosle-on-raj-thackrey-uddhav-thackrey-togater-she-says-i-only-know-ashish-shelar-i-don-t-know-any-other-politician-1366511</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/live-telecast-of-ganeshotsav-events-minister/articleshow/122770675.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>https://aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/mumbai-bjp-new-president-appointed-three-time-mla-ameet-satam-bmc-elections-big-challenge/4109409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-election-commission-allegations-devendra-fadnavis-ashish-shelar-response-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!bharat/ahead-of-bmc-polls-mla-ameet-satam-named-new-mumbai-bjp-chief-hindi-news-hin25082501591</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>https://thecsrjournal.in/maharashtra-declares-ganeshotsav-as-state-festival-hindi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-andheri-west-mla-ameet-satam-appointed-mumbai-bjp-chief-ahead-of-bmc-polls-know-all/articleshow/123499476.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/savarkar-song-anadi-me-anant-me-gets-inspirational-song-award-maharashtra-government-makes-a-big-announcement-ntc-dskc-2176549-2025-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-devendra-fadnavis-govt-also-participates-in-ganeshotsav-2025-made-a-big-announcement/articleshow/122785708.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-ganeshotsav-declared-state-festival-of-maharashtra-minister-ashish-shelar-expressed-happiness-news-hindi-1-735521-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>https://www.prabhasakshi.com/national/fadnavis-governments-big-decision-ganeshotsav-gets-state-festival-status-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>https://hindicurrentaffairs.adda247.com/maharashtra-government-declares-ganeshotsav-as-state-festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://dainiksaveratimes.com/big-1/ganeshotsav-gets-status-state-festival-in-maharashtra-fadnavis-government/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/lifestyle/festivals-events/ganeshotsav-now-maharashtras-official-state-festival-govt-to-fund-celebrations-2689983.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://bharat24live.com/news/devajit-saikia-replaces-jay-shah-as-bcci-secretary</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://www.outlookhindi.com/country/state/will-the-method-of-immersion-of-ganpati-bappa-change-now-read-the-new-policy-of-maharashtra-government-101125</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A102"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,707 +438,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-suburban-guardian-minister-ashish-shelar-says-govt-will-frame-policy-to-grant-occupation-certificate-to-more-than-25000-buildings/articleshow/123833814.cms</t>
+          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pak-asia-cup-match-ashish-shelar/ar-AA1MzRl0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-slams-shiv-sena-ubt-for-opposing-india-pakistan-asia-cup-match-23593693</t>
+          <t>https://www.ptinews.com/editor-detail/People-understood-govt%E2%80%99s-stand-on-India-Pak-Asia-Cup-match-Ashish-Shelar/2916156</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625230-cricket-politics-and-controversies-maharashtra-minister-defends-india-pakistan-match?amp</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/world/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/ar-AA1MuAh8</t>
+          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/25k-bldgs-to-benefit-from-new-policy-of-speedy-ocs-101757618615331.html</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612?amp=1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.telegraphindia.com/amp/india/maharashtra-opposition-slams-bjp-bcci-how-can-cricket-and-blood-flow-together/cid/2122820</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/Over-25-000-buildings-without-OC-in-Mumbai-to-be-regularised-under-new-policy-Minister/2905701</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-pushes-for-koliwadas-to-be-demarcated-entered-in-dcpr-101757705038590.html</t>
+          <t>https://www.bakharlive.com/mumbai/minister-ashish-shelars-announcement-gives-new-impetus-to-the-cinema-business-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/infrastructure/koliwada-demarcations-likely-to-be-incorporated-into-development-plan-89978</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3625616-cricket-diplomacy-or-dispute-thackeray-vs-bjp-on-india-pakistan-fixture?amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://globalgreenews.com/2025/09/14/maharashtra-to-launch-survey-of-3000-historic-wells-minister-ashish-shelar/</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-mumbai-live/20250913/281694030924555</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/over-25000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-10441211</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/asia-cup-match-we-have-no-enmity-with-cricket-pakistan-you-will-not-be-spared-shiv-sena-ubt-leader-protested-against-india-pak-match-broke-tv-news-295117</t>
+          <t>https://mahasamvad.in/178553/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/mumbais-25000-buildings-to-get-occupation-certificates-under-new-policy/123842401</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/big-decision-on-mumbais-koliwadas-adv-ashish-shelar-gives-60-day-ultimatum-ok/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.amp.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553?business-real-estate-breakingnews</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announce-process-to-benefits-of-government-services-and-schemes-on-whatsapp-1478023.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-mumbai-pune-nagpur-kolhapur-breaking-news-asc-95-5366993/</t>
+          <t>https://mahasamvad.in/178660/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%95-%E0%A4%B3-%E0%A4%B5-%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF/ar-AA1MsSIk</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ashish-shelar-orders-registration-of-coastal-villages-in-dp-after-demarcation/articleshow/123862832.cms</t>
+          <t>https://www.timemaharashtra.com/entertainment/cultural-affairs-minister-adv-ashish-shelar-inaugurated-the-dadasaheb-phalke-film-rasaswad-mandal/132991/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-25000-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%93%E0%A4%B8-%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B8-%E0%A4%AB-%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B5-%E0%A4%AD-%E0%A4%97-2-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%A8%E0%A4%88-%E0%A4%A8-%E0%A4%A4/ar-AA1MnFDI</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/political-riot-before-india-vs-pakistan-match-when-aimim-raised-questions-on-the-contest-bjp-retaliated-2025-09-12</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-directs-to-record-demarcation-of-mumbai-koliwada-gaothan-in-development-plan-zws-70-5368411/lite/</t>
+          <t>https://www.msn.com/en-in/news/India/good-news-for-mumbaikars-new-weekly-bandra-terminus-lalkuan-express-flagged-off-check-details/ar-AA1scS2L?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/plans-should-be-made-to-make-75-villages-in-the-state-smart-villages-information-technology-minister-ashish-shelar/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/service-fortnight-in-the-state-from-17th-september-to-2nd-october-minister-adv-ashish-shelar-75-villages-in-th.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475/amp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5%E0%A4%9C-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%A4%E0%A4%82-%E0%A4%B5-%E0%A4%9F%E0%A4%A4-%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%98%E0%A4%B0-%E0%A4%A4%E0%A4%B2-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%B2%E0%A4%A2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%B5%E0%A4%A3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%98-%E0%A4%B0-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE%E0%A4%A4/ar-AA1sXOeV?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://news18marathi.com/news/mobile-setu-kendra-facility-launched-under-seva-pandharwada-campaign-in-mumbai-suburbs-local18-1482559.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%9A-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%97%E0%A5%82%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%A4%E0%A4%AC%E0%A5%8D%E0%A4%AC%E0%A4%B2-25-000-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-oc-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8%E0%A4%9A-%E0%A4%AE-%E0%A4%9F%E0%A4%B2-%E0%A4%86%E0%A4%A4-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A4%A3/ar-AA1MtCiQ</t>
+          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-%E0%A4%B2-%E0%A4%96-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A3-%E0%A4%85%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%98%E0%A4%B0-25-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%82%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%A8-oc-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%AE-%E0%A4%95%E0%A4%B3/ar-AA1Mpmwg?ocid=finance-verthp-feeds</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sit-formed-to-investigate-the-issue-of-fake-maps-of-development-plan-lands-in-kandivali-malad-and-borivali-mumbai-maharashtra-news-mhs25091403049</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/amp_articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-shah-at-lalbaugcha-raja-%E0%A4%97-%E0%A4%82%E0%A4%A1%E0%A4%B8-%E0%A4%A8-%E0%A4%A4%E0%A4%B5-%E0%A4%B2-%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B2-%E0%A4%B2%E0%A4%AC-%E0%A4%97%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B2/ar-AA1LwAZa?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://jantaserishta.com/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178159/</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/vandre-east/mumbai-deputy-meeting-in-the-office-of-cultural-affairs-minister-shelar-15379719</t>
+          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-12-political-news-in-marathi-938622</t>
+          <t>https://politicalmaharashtra.in/is-the-issue-of-hyderabad-gazette-on-the-agenda-banjara-dhanagar-new-dispute-97852/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://www.ptinews.com/story/national/nepal-police-re-arrest-3-723-jail-inmates-who-escaped-during-gen-z-protests/2914554</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/borivali/mumbai-sub-policy-to-issue-occupancy-certificate-soon-15382525</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/versova/mumbai-sub-demarcation-of-koliwadas-is-mandatory-in-dp-15383355</t>
+          <t>http://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/ashish-shelar-assured-on-the-policy-of-issuing-ocs-to-more-than-25000-buildings/</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-problems-of-residents-of-buildings-without-oc-to-be-resolved-soon-as-government-making-policy-to-give-oc-for-25000-buildings-article-152787618</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178213/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-%E0%A4%B2-%E0%A4%96-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A3-%E0%A4%85%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%98%E0%A4%B0-25-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%82%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%A8-oc-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%AE-%E0%A4%95%E0%A4%B3/ar-AA1Mpmwg</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/locals-felicitated-mla-atul-bhosale-pune-bangalore-highway-permanent-road-crossing-between-pillars-75-and-76-sud-02-5370036/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AD-%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B8%E0%A4%B2-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A4%97-%E0%A4%AE-%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8/ar-AA1I49FT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/bjp-protests-against-congress-in-vasai-strong-reaction-to-rahul-gandhis-statement.html</t>
+          <t>https://www.lokmattimes.com/business/samsung-to-launch-galaxy-s25-fe-tab-s11-buds3-fe-on-sept-19/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cidco-housing-scam-developers-denied-oc-ocd-94-5366496/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/thane-lok-adalat-awards-1-crore-compensation-ocd-94-5370089/</t>
+          <t>http://www.acnnewswire.com/press-release/All/102672/InfoComm-India-2025-Sets-New-B</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maratha-reservation-gr-will-not-be-withdrawn-vikhe-patil-rat16</t>
+          <t>https://www.devdiscourse.com/article/education/3628243-trump-to-inject-500-million-into-black-colleges-and-charter-schools-nytimes-report-says?amp</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/14/the-99th-all-india-marathi-literature-conference-will-be-held-under-the-chairmanship-of-panipatkar-vishwas-pat.html</t>
+          <t>https://www.lokmattimes.com/maharashtra/raj-thackeray-criticise-jay-shah-and-union-home-minister-amit-shah-over-india-vs-pakistan-match-in-asia-cup-2025-a517/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/hindu-homeowner-fatally-attacked-by-religious-fanatics-in-nayanagar-area.html</t>
+          <t>https://www.lokmattimes.com/business/india-eyes-global-leadership-in-shipbuilding-with-policy-push-alliances-sp-global/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/passengers-suffer-due-to-encroachment-at-municipal-bus-stops.html</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-girlfriend-booked-for-abetment-of-suicide-after-22-year-old-boyfriend-hangs-himself-in-govandi-a522/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/signature-campaign-for-dj-ban-in-pune-citizens-troubled-by-noise-pollution/articleshow/123864275.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/marathwada-floods-dozens-stranded-as-heavy-rains-trigger-rescue-operations-watch-video-a525/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/trimbakeshwar-trust-puzzled-by-collector-letter-nashik-ocd-94-5370024/lite/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/mumbai-buildings-oc-policy-govts-decision-to-provide-occupancy-certificates-to-25-000-buildings-036983.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/raj-thackeray-seems-to-have-upper-hand-in-alliance-moves-with-uddhav-claim-political-analysts/amp_articleshow/123881278.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/amp_articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-to-launch-survey-of-3000-historic-wells-minister-ashish-shelar/</t>
+          <t>https://www.aninews.in/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level20250915142133?amp=1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/will-watch-in-burqa-nitesh-rane-mocks-aaditya-thackeray-over-indiapakistan-match-watch/amp_articleshow/123868392.cms</t>
+          <t>https://www.lokmattimes.com/business/et-leadership-excellence-awards2025-acknowledging-the-leaders/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-pushes-for-koliwadas-to-be-demarcated-entered-in-dcpr-101757705038590-amp.html</t>
+          <t>https://www.msn.com/en-in/sports/cricket/how-ispl-s-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/ar-AA1MJR7I</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3625616-cricket-diplomacy-or-dispute-thackeray-vs-bjp-on-india-pakistan-fixture</t>
+          <t>https://www.lokmattimes.com/international/un-envoy-asks-international-engagement-with-afghanistan-to-continue-amid-political-crisis/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/shelar-criticised-shiv-sena-ubatha-for-opposing-india-pakistan-match-in-asia-cup/867624/?amp</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%9F-%E0%A4%82%E0%A4%97-bjp-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A5%E0%A5%88%E0%A4%82%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MqqOf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbaikars-good-news-25000-buildings-without-oc-in-mumbai-urban-development-department-implement-new-policy-to-regularise/articleshow/123836698.cms</t>
+          <t>https://acnnewswire.com/press-release/japanese/102672/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-15-september-2025-in-hindi-todays-top-news</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ashish-shelar-orders-registration-of-coastal-villages-in-dp-after-demarcation/amp_articleshow/123862832.cms</t>
+          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharshtra-co-guardian-ministers-gets-power-cm-fadnavis-said-said-they-also-solve-problems-know-all/articleshow/123869141.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/mumbais-over-25000-buildings-to-receive-occupancy-certificates-online-process-starts-from-october-2/articleshow/123845042.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/assistance-of-rupees-73-crores-announced-for-farmers-affected-due-to-unseasonal-rain/articleshow/123862852.cms</t>
+          <t>https://www.devdiscourse.com/article/education/3628122-sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level?amp</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/pune-gutkha-smuggling-through-railway-parcel-three-arrested/articleshow/123864228.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/punes-defense-production-companies-double-growth-rapid-development-of-the-sector/articleshow/123862862.cms</t>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-problems-of-residents-of-buildings-without-oc-to-be-resolved-soon-as-government-making-policy-to-give-oc-for-25000-buildings-article-152787618/amp</t>
+          <t>https://www.thejbt.com/india/pm-modi-75th-birthday-pm-modi-birthday-was-celebrated-with-service-and-dedication-a-shower-of-public-welfare-schemes-across-the-country-news-295329</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Policy-regarding-issuance-of-occupancy-certificates-to-more-than-25000-buildings-in-Mumbai.html</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/cm-himmat-biswa-sharmas-comments-on-sit-revelations-of-gaurav-gogoi/amp_articleshow/123862876.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-distributed-powers-of-guardian-minister-to-co-guardian-ministers-in-maharashtra-vru98</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/cricket/india-pakistan-asia-cup-cricket-match-opposition-parties-slam-bjp-bcci-for-playing-with-the-enemy/amp</t>
+          <t>https://itbusinessnet.com/2025/09/infocomm-india-2025-sets-new-benchmark-delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learning/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://udayavani.com/sports/india-pakistan-asia-cup-cricket-match-oppn-parties-slam-bjp-bcci-for-playing-with-the-enemy-360830?lang=en</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://newstrailindia.com/inner.php?id=28297</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/the-story-of-the-terrified-naxalites-a-plea-for-peace-talks.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/musical-program-concluded-in-memory-of-bharat-ratna-ustad-bismillah-khan/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-kala-samvads-exhibition-inaugurated/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://bharatexpress.com/india/mumbai-resonates-ustad-bismillah-khan-music-566205/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhupen-hazarika-centenary-mumbai-hosts-grand-tribute-top-artists-honour-musical-legend/articleshow/123845988.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://indiaeducationdiary.in/shivsanskar-mahotsav-2025-showcases-chhatrapati-shivaji-maharajs-timeless-wisdom-through-art-poetry-and-dialogue/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625263-blind-tattoo-virtuoso-igor-mikhaylovs-mastery-of-ink-and-imagination?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-gives-nod-for-bmc-run-nursing-college-in-bandra/articleshow/123883610.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3626431-cricket-diplomacy-controversy-over-india-pakistan-match?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3624103-mumbai-buildings-set-for-occupancy-boost-new-policy-in-place</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://www.uniindia.com/news/west/administration-mum-occupancy-certificate/3574275.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>https://outlookhindi.com/politics/regional-team/ashish-shelar-criticised-shiv-sena-ubatha-for-opposing-india-pakistan-match-in-asia-cup-102301</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/other/ind-vs-pak-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AA-%E0%A4%95-%E0%A4%AE%E0%A5%88%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%A4-bjp-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MqePu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/articleshow/123872340.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/as-india-pakistan-take-to-field-in-dubai-opposition-parties-hit-the-streets-3727488</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>https://bharatexpress.com/india/mumbai-resonates-ustad-bismillah-khan-music-566205</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/time-to-play-biz-t-20-with-australia-says-maharashtra-cm-devendra-fadnavis/articleshow/123833319.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11?src=top-subnav</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625230-cricket-politics-and-controversies-maharashtra-minister-defends-india-pakistan-match</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>https://madhyamamonline.com/amp/india/opposition-slams-bjp-bcci-over-india-pakistan-asia-cup-match-1446713</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>https://www.orissapost.com/opposition-slams-bjp-bcci-over-india-pakistan-asia-cup-match/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>https://theshillongtimes.com/2025/09/12/frustration-and-moral-decline-bjp-slams-congress-over-ai-video-featuring-pm-modis-mother/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/entertainment/bollywood-news/photo/tiff-2025-pratik-gandhi-huma-qureshi-tom-felton-anurag-kashyap-hansal-mehta-107275/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/entertainment/bollywood-news/photo/anurag-kashyap-birthday-2025-adorable-pics-of-filmmaker-with-daughter-aaliyah-107276/13</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,28 +445,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/People-understood-govt%E2%80%99s-stand-on-India-Pak-Asia-Cup-match-Ashish-Shelar/2916156</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612?amp=1</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
@@ -480,56 +480,56 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%96-%E0%A4%89%E0%A4%A6%E0%A4%AF%E0%A4%A8%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%AA-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0/ar-AA1MVLVU</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.bakharlive.com/mumbai/minister-ashish-shelars-announcement-gives-new-impetus-to-the-cinema-business-in-maharashtra/</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
@@ -543,453 +543,467 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.amp.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178660/</t>
+          <t>https://mahasamvad.in/179631/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
+          <t>https://mahasamvad.in/178660/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/entertainment/cultural-affairs-minister-adv-ashish-shelar-inaugurated-the-dadasaheb-phalke-film-rasaswad-mandal/132991/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-skips-shivaji-park-gymkhana-inauguration-fueling-raj-thackeray-political-rift-speculation-and-discussions-on-their-strained-friendship-1386004</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/good-news-for-mumbaikars-new-weekly-bandra-terminus-lalkuan-express-flagged-off-check-details/ar-AA1scS2L?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475/amp</t>
+          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/news/mobile-setu-kendra-facility-launched-under-seva-pandharwada-campaign-in-mumbai-suburbs-local18-1482559.html</t>
+          <t>https://www.marathi.hindusthanpost.com/social/bjp-insists-on-gargai-dam-guardian-minister-gives-instructions-to-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
+          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pakistan-asia-cup-match-ashish-shelar/ar-AA1Mzlfh</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/amp_articleshow/123916817.cms</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/is-the-issue-of-hyderabad-gazette-on-the-agenda-banjara-dhanagar-new-dispute-97852/</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/nepal-police-re-arrest-3-723-jail-inmates-who-escaped-during-gen-z-protests/2914554</t>
+          <t>https://www.jpnnews.in/2025/09/Mumbaikars-year-round-water-worries-are-over.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.jpnnews.in/2025/09/Deploy-more-traffic%20police-to-avoid-traffic-jams.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>http://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://www.jpnnews.in/2025/09/mumbai-colaba-aarey-metro-line-3-full-route-service-from-september-30.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AD-%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B8%E0%A4%B2-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A4%97-%E0%A4%AE-%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8/ar-AA1I49FT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-celebrity-stylist-thompsun-fernandes-gives-150-free-haircuts-at-bandra-fair</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/samsung-to-launch-galaxy-s25-fe-tab-s11-buds3-fe-on-sept-19/</t>
+          <t>https://up18news.com/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-pronade-to-celebrate-pm-modi-jis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>http://www.acnnewswire.com/press-release/All/102672/InfoComm-India-2025-Sets-New-B</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3628243-trump-to-inject-500-million-into-black-colleges-and-charter-schools-nytimes-report-says?amp</t>
+          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/raj-thackeray-criticise-jay-shah-and-union-home-minister-amit-shah-over-india-vs-pakistan-match-in-asia-cup-2025-a517/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/india-eyes-global-leadership-in-shipbuilding-with-policy-push-alliances-sp-global/</t>
+          <t>https://dainikekmat.com/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B8-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A4%B2%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8%E0%A4%BE/117558/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-girlfriend-booked-for-abetment-of-suicide-after-22-year-old-boyfriend-hangs-himself-in-govandi-a522/</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/marathwada-floods-dozens-stranded-as-heavy-rains-trigger-rescue-operations-watch-video-a525/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/amp_articleshow/123971975.cms</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level20250915142133?amp=1</t>
+          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/et-leadership-excellence-awards2025-acknowledging-the-leaders/</t>
+          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/how-ispl-s-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/ar-AA1MJR7I</t>
+          <t>https://www.tribuneindia.com/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/international/un-envoy-asks-international-engagement-with-afghanistan-to-continue-amid-political-crisis/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%9F-%E0%A4%82%E0%A4%97-bjp-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A5%E0%A5%88%E0%A4%82%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MqqOf</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://acnnewswire.com/press-release/japanese/102672/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
+          <t>https://www.bignewsnetwork.com/news/278577272/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
+          <t>https://www.moneylife.in/article/25000-buildings-without-ocs-in-mumbai-maharashtra-moves-to-regularise-suburban-homes/78347.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
+          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.bignewsnetwork.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3628122-sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level?amp</t>
+          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
+          <t>https://www.bignewsnetwork.com/news/278593336/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbai-coastal-road-promenade-to-celebrate-pm-modi-ji-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/pm-modi-75th-birthday-pm-modi-birthday-was-celebrated-with-service-and-dedication-a-shower-of-public-welfare-schemes-across-the-country-news-295329</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.adgully.com/post/6854/india-today-conclave-mumbai-2025-set-to-bring-together-indias-leading-voices-on-sept-25-26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/zeenat-shabrin-becomes-first-woman-president-of-mumbai-youth-congress</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://itbusinessnet.com/2025/09/infocomm-india-2025-sets-new-benchmark-delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learning/</t>
+          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/the-story-of-the-terrified-naxalites-a-plea-for-peace-talks.html</t>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
         </is>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,63 +438,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pak-asia-cup-match-ashish-shelar/ar-AA1MzRl0</t>
+          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
+          <t>https://www.uniindia.com/news/west/politics-maha-minister/3584617.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%96-%E0%A4%89%E0%A4%A6%E0%A4%AF%E0%A4%A8%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%AA-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0/ar-AA1MVLVU</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
@@ -508,28 +508,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
@@ -543,469 +543,336 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179631/</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178660/</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-skips-shivaji-park-gymkhana-inauguration-fueling-raj-thackeray-political-rift-speculation-and-discussions-on-their-strained-friendship-1386004</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
+          <t>https://mahasamvad.in/179588/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://mahasamvad.in/179631/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
+          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/bjp-insists-on-gargai-dam-guardian-minister-gives-instructions-to-commissioner/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pakistan-asia-cup-match-ashish-shelar/ar-AA1Mzlfh</t>
+          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/cancer-treatment-centers-will-be-opened-in-every-district-of-maharashtra-state-government-decides-125091600026_1.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Mumbaikars-year-round-water-worries-are-over.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Deploy-more-traffic%20police-to-avoid-traffic-jams.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/mumbai-colaba-aarey-metro-line-3-full-route-service-from-september-30.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-celebrity-stylist-thompsun-fernandes-gives-150-free-haircuts-at-bandra-fair</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://up18news.com/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-pronade-to-celebrate-pm-modi-jis-75th-birthday/</t>
+          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B8-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A4%B2%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8%E0%A4%BE/117558/</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pm-s-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278577272/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://www.moneylife.in/article/25000-buildings-without-ocs-in-mumbai-maharashtra-moves-to-regularise-suburban-homes/78347.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278593336/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbai-coastal-road-promenade-to-celebrate-pm-modi-ji-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://www.adgully.com/post/6854/india-today-conclave-mumbai-2025-set-to-bring-together-indias-leading-voices-on-sept-25-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/zeenat-shabrin-becomes-first-woman-president-of-mumbai-youth-congress</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
+          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
@@ -459,84 +459,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/politics-maha-minister/3584617.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178553/</t>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
         </is>
       </c>
     </row>
@@ -557,322 +557,364 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/ubatha-group-will-soon-merge-with-congress-navnath-bans-counterattack.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179588/</t>
+          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://www.lokmattimes.com/national/eight-mlas-take-oath-as-ministers-in-meghalaya-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179631/</t>
+          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
+          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/cancer-treatment-centers-will-be-opened-in-every-district-of-maharashtra-state-government-decides-125091600026_1.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.lokmattimes.com/aurangabad/technical-glitch-leaves-8-of-taxpayers-unable-to-file-income-tax-returns-1/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/national/bjp-leader-tarun-chugh-takes-exception-to-rahuls-confrontation-with-punjab-police</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://www.lokmattimes.com/national/baseless-incomplete-info-bjp-leader-hits-back-at-kharges-gst-20-criticism/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
+          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pm-s-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
+          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.aninews.in/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
+          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,245 +438,245 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://marathi.ndtv.com/cities/shiv-smarak-and-shiv-mudra-to-be-erected-on-the-road-leading-to-navi-mumbai-international-airport-9288363</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/ubatha-group-will-soon-merge-with-congress-navnath-bans-counterattack.html</t>
+          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://www.lokmattimes.com/entertainment/jolly-llb-3-box-office-collection-day-1-akshay-kumar-arshad-warsis-film-earns-rs-1275-crore-on-opening-day-a507/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/eight-mlas-take-oath-as-ministers-in-meghalaya-cabinet/</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
+          <t>https://ndtv.in/india/pm-modi-75th-birthday-leaders-congratulated-know-who-said-what-9290156</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
@@ -690,35 +690,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/technical-glitch-leaves-8-of-taxpayers-unable-to-file-income-tax-returns-1/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
+          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
+          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
         </is>
       </c>
     </row>
@@ -739,180 +739,152 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leader-tarun-chugh-takes-exception-to-rahuls-confrontation-with-punjab-police</t>
+          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/baseless-incomplete-info-bjp-leader-hits-back-at-kharges-gst-20-criticism/</t>
+          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.lokmattimes.com/national/pm-modi-to-visit-arunachal-pradesh-tripura-today-to-launch-projects-worth-over-rs-5100-cr/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
+          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
+          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
+          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
+          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
+          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
+          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
         <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>

--- a/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links_Ashish Shelar_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,453 +438,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://www.lokmattimes.com/entertainment/akshay-kumars-wit-and-humour-leaves-kapil-sharma-speechless-on-his-own-ott-show/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/shiv-smarak-and-shiv-mudra-to-be-erected-on-the-road-leading-to-navi-mumbai-international-airport-9288363</t>
+          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/jolly-llb-3-box-office-collection-day-1-akshay-kumar-arshad-warsis-film-earns-rs-1275-crore-on-opening-day-a507/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/hardoi/man-attacked-on-coconut-seller-boy-with-sharp-object-banka-in-hardoi-for-not-giving-pen/2929179</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-75th-birthday-leaders-congratulated-know-who-said-what-9290156</t>
+          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.lokmattimes.com/national/bettiah-kidnapping-6-year-old-child-abducted-from-bihar-school-by-man-posing-as-parent-rescued-within-6-hours-a517/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-amaal-mallik-shehbaz-badeshahs-prank-goes-wrong/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/pm-modi-to-visit-arunachal-pradesh-tripura-today-to-launch-projects-worth-over-rs-5100-cr/</t>
+          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-round-of-congratulations-on-pm-modis-birthday-many-leaders-gave-best-wishes-news-hindi-1-753396-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
         <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
